--- a/code/experiment/1024chunk_Qwen3_10topk_Y.xlsx
+++ b/code/experiment/1024chunk_Qwen3_10topk_Y.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532C3A7E-395A-435B-8C85-FD4825EBFC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1AEBF4-E0D4-44EF-A595-F7695626CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -296,9 +296,6 @@
 来自: [Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models, 第14页, Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models_chunk_013]</t>
   </si>
   <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
   </si>
   <si>
@@ -640,6 +637,10 @@
   </si>
   <si>
     <t>【不可回答类平均值】</t>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1083,7 +1084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="336" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="168" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -1303,7 +1304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1347,7 +1348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1391,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1479,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1523,7 +1524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="196" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
@@ -1699,7 +1700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="406" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>59</v>
       </c>
@@ -1831,7 +1832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>68</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
@@ -1921,16 +1922,16 @@
     </row>
     <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1965,16 +1966,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -2007,18 +2008,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="224" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2051,18 +2052,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2097,16 +2098,16 @@
     </row>
     <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2139,18 +2140,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2185,16 +2186,16 @@
     </row>
     <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2227,18 +2228,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="E28" s="2">
         <v>0</v>
@@ -2271,18 +2272,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="182" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -2315,18 +2316,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="224" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2359,18 +2360,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="266" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -2403,18 +2404,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2449,16 +2450,16 @@
     </row>
     <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2491,18 +2492,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2535,18 +2536,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -2581,16 +2582,16 @@
     </row>
     <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -2625,16 +2626,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2669,16 +2670,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -2713,16 +2714,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -2757,16 +2758,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2801,16 +2802,16 @@
     </row>
     <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2845,16 +2846,16 @@
     </row>
     <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="E42" s="2">
         <v>1</v>
@@ -2889,16 +2890,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2931,265 +2932,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="J44" s="2">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2">
+        <v>1</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="56" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J44" s="2">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" s="2">
-        <v>1</v>
-      </c>
-      <c r="M44" s="2">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="140" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2">
+        <v>1</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J45" s="2">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2">
-        <v>1</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" s="2">
-        <v>0</v>
-      </c>
-      <c r="O45" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="84" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="70" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J46" s="2">
-        <v>1</v>
-      </c>
-      <c r="K46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" s="2">
-        <v>1</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2">
-        <v>0</v>
-      </c>
-      <c r="O46" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="210" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="J47" s="2">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2">
+        <v>1</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J47" s="2">
-        <v>1</v>
-      </c>
-      <c r="K47" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" s="2">
-        <v>1</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-      <c r="N47" s="2">
-        <v>0</v>
-      </c>
-      <c r="O47" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="98" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="J48" s="2">
+        <v>1</v>
+      </c>
+      <c r="K48" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2">
+        <v>1</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J48" s="2">
-        <v>1</v>
-      </c>
-      <c r="K48" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" s="2">
-        <v>1</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="98" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="J49" s="2">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="56" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J49" s="2">
-        <v>1</v>
-      </c>
-      <c r="K49" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" s="2">
-        <v>1</v>
-      </c>
-      <c r="M49" s="2">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="126" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="J50" s="2">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2">
+        <v>1</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J50" s="2">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" s="2">
-        <v>1</v>
-      </c>
-      <c r="M50" s="2">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="126" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2">
+        <v>1</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0</v>
+      </c>
+      <c r="N51" s="2">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2">
-        <v>1</v>
-      </c>
-      <c r="M51" s="2">
-        <v>0</v>
-      </c>
-      <c r="N51" s="2">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="28" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3228,9 +3229,9 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3272,9 +3273,9 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>53</v>
@@ -3316,12 +3317,12 @@
         <v>0.36363636363636365</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3360,12 +3361,12 @@
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3404,12 +3405,12 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
